--- a/04-Development-and-Quality-Assurance/Evaluation-Testing/Logs/Fedora/Fedora_Data.xlsx
+++ b/04-Development-and-Quality-Assurance/Evaluation-Testing/Logs/Fedora/Fedora_Data.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29415"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="40" documentId="11_107F4D40C652DF2A2190C800EC9AC7EE6E8982F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E188BC96-24BA-451A-8285-136E985A5FE6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
@@ -19,11 +19,11 @@
     <sheet name="IPv6 - TCP" sheetId="3" r:id="rId4"/>
     <sheet name="IPv6 - UDP" sheetId="4" r:id="rId5"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId6"/>
-  </externalReferences>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -41,6 +41,51 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="39">
+  <si>
+    <t>IPv4</t>
+  </si>
+  <si>
+    <t>IPv6</t>
+  </si>
+  <si>
+    <t>IPv4 TCP</t>
+  </si>
+  <si>
+    <t>IPv4 UDP</t>
+  </si>
+  <si>
+    <t>IPv6 TCP</t>
+  </si>
+  <si>
+    <t>IPv6 UDP</t>
+  </si>
+  <si>
+    <t>Packet Size</t>
+  </si>
+  <si>
+    <t>TCP Average Delay</t>
+  </si>
+  <si>
+    <t>TCP Jitter</t>
+  </si>
+  <si>
+    <t>TCP Bitrate</t>
+  </si>
+  <si>
+    <t>TCP Packet Loss</t>
+  </si>
+  <si>
+    <t>UDP Average Delay</t>
+  </si>
+  <si>
+    <t>UDP Jitter</t>
+  </si>
+  <si>
+    <t>UDP Bitrate</t>
+  </si>
+  <si>
+    <t>UDP Packet Loss</t>
+  </si>
   <si>
     <t>128</t>
   </si>
@@ -70,9 +115,6 @@
   </si>
   <si>
     <t>Average packet rate (pkt/s)</t>
-  </si>
-  <si>
-    <t>Packet Size</t>
   </si>
   <si>
     <t>Average Delay</t>
@@ -116,54 +158,12 @@
   <si>
     <t>1536</t>
   </si>
-  <si>
-    <t>IPv4</t>
-  </si>
-  <si>
-    <t>IPv6</t>
-  </si>
-  <si>
-    <t>IPv4 TCP</t>
-  </si>
-  <si>
-    <t>IPv4 UDP</t>
-  </si>
-  <si>
-    <t>IPv6 TCP</t>
-  </si>
-  <si>
-    <t>IPv6 UDP</t>
-  </si>
-  <si>
-    <t>TCP Average Delay</t>
-  </si>
-  <si>
-    <t>TCP Jitter</t>
-  </si>
-  <si>
-    <t>TCP Bitrate</t>
-  </si>
-  <si>
-    <t>TCP Packet Loss</t>
-  </si>
-  <si>
-    <t>UDP Average Delay</t>
-  </si>
-  <si>
-    <t>UDP Jitter</t>
-  </si>
-  <si>
-    <t>UDP Bitrate</t>
-  </si>
-  <si>
-    <t>UDP Packet Loss</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -213,10 +213,10 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -9207,753 +9207,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Sheet1"/>
-      <sheetName val="IPv4 - TCP"/>
-      <sheetName val="IPv4 - UDP"/>
-      <sheetName val="IPv6 - TCP"/>
-      <sheetName val="IPv6 - UDP"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="6">
-          <cell r="C6" t="str">
-            <v>TCP Average Delay</v>
-          </cell>
-          <cell r="D6" t="str">
-            <v>TCP Jitter</v>
-          </cell>
-          <cell r="E6" t="str">
-            <v>TCP Bitrate</v>
-          </cell>
-          <cell r="F6" t="str">
-            <v>TCP Packet Loss</v>
-          </cell>
-          <cell r="I6" t="str">
-            <v>UDP Average Delay</v>
-          </cell>
-          <cell r="J6" t="str">
-            <v>UDP Jitter</v>
-          </cell>
-          <cell r="K6" t="str">
-            <v>UDP Bitrate</v>
-          </cell>
-          <cell r="L6" t="str">
-            <v>UDP Packet Loss</v>
-          </cell>
-          <cell r="T6" t="str">
-            <v>TCP Average Delay</v>
-          </cell>
-          <cell r="U6" t="str">
-            <v>TCP Jitter</v>
-          </cell>
-          <cell r="V6" t="str">
-            <v>TCP Bitrate</v>
-          </cell>
-          <cell r="W6" t="str">
-            <v>TCP Packet Loss</v>
-          </cell>
-          <cell r="Z6" t="str">
-            <v>UDP Average Delay</v>
-          </cell>
-          <cell r="AA6" t="str">
-            <v>UDP Jitter</v>
-          </cell>
-          <cell r="AB6" t="str">
-            <v>UDP Bitrate</v>
-          </cell>
-          <cell r="AC6" t="str">
-            <v>UDP Packet Loss</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="B7">
-            <v>128</v>
-          </cell>
-          <cell r="C7">
-            <v>5.1900000000000004E-4</v>
-          </cell>
-          <cell r="D7">
-            <v>9.8499999999999995E-5</v>
-          </cell>
-          <cell r="E7">
-            <v>17245.820185099998</v>
-          </cell>
-          <cell r="F7">
-            <v>0</v>
-          </cell>
-          <cell r="I7">
-            <v>3.9450000000000005E-4</v>
-          </cell>
-          <cell r="J7">
-            <v>4.6299999999999994E-5</v>
-          </cell>
-          <cell r="K7">
-            <v>17456.933687000001</v>
-          </cell>
-          <cell r="L7">
-            <v>0.09</v>
-          </cell>
-          <cell r="S7">
-            <v>128</v>
-          </cell>
-          <cell r="T7">
-            <v>5.9690000000000003E-4</v>
-          </cell>
-          <cell r="U7">
-            <v>9.7E-5</v>
-          </cell>
-          <cell r="V7">
-            <v>17261.783222099999</v>
-          </cell>
-          <cell r="W7">
-            <v>0</v>
-          </cell>
-          <cell r="Z7">
-            <v>1.305E-4</v>
-          </cell>
-          <cell r="AA7">
-            <v>4.6099999999999996E-5</v>
-          </cell>
-          <cell r="AB7">
-            <v>17449.604368099997</v>
-          </cell>
-          <cell r="AC7">
-            <v>5.2000000000000005E-2</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="B8">
-            <v>256</v>
-          </cell>
-          <cell r="C8">
-            <v>5.1509999999999989E-4</v>
-          </cell>
-          <cell r="D8">
-            <v>9.0400000000000015E-5</v>
-          </cell>
-          <cell r="E8">
-            <v>34804.3220115</v>
-          </cell>
-          <cell r="F8">
-            <v>0</v>
-          </cell>
-          <cell r="I8">
-            <v>4.3400000000000003E-4</v>
-          </cell>
-          <cell r="J8">
-            <v>4.7099999999999993E-5</v>
-          </cell>
-          <cell r="K8">
-            <v>34942.620202500002</v>
-          </cell>
-          <cell r="L8">
-            <v>6.0000000000000012E-2</v>
-          </cell>
-          <cell r="S8">
-            <v>256</v>
-          </cell>
-          <cell r="T8">
-            <v>5.5079999999999994E-4</v>
-          </cell>
-          <cell r="U8">
-            <v>9.0300000000000013E-5</v>
-          </cell>
-          <cell r="V8">
-            <v>34817.985176900009</v>
-          </cell>
-          <cell r="W8">
-            <v>0</v>
-          </cell>
-          <cell r="Z8">
-            <v>1.651E-4</v>
-          </cell>
-          <cell r="AA8">
-            <v>4.7000000000000004E-5</v>
-          </cell>
-          <cell r="AB8">
-            <v>34920.658910500002</v>
-          </cell>
-          <cell r="AC8">
-            <v>6.4000000000000015E-2</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="B9">
-            <v>384</v>
-          </cell>
-          <cell r="C9">
-            <v>8.8909999999999998E-4</v>
-          </cell>
-          <cell r="D9">
-            <v>8.7799999999999993E-5</v>
-          </cell>
-          <cell r="E9">
-            <v>52601.005454100006</v>
-          </cell>
-          <cell r="F9">
-            <v>0</v>
-          </cell>
-          <cell r="I9">
-            <v>4.3939999999999995E-4</v>
-          </cell>
-          <cell r="J9">
-            <v>4.4600000000000007E-5</v>
-          </cell>
-          <cell r="K9">
-            <v>52154.577835999997</v>
-          </cell>
-          <cell r="L9">
-            <v>6.0000000000000012E-2</v>
-          </cell>
-          <cell r="S9">
-            <v>384</v>
-          </cell>
-          <cell r="T9">
-            <v>9.2360000000000012E-4</v>
-          </cell>
-          <cell r="U9">
-            <v>8.8299999999999978E-5</v>
-          </cell>
-          <cell r="V9">
-            <v>52553.033332400002</v>
-          </cell>
-          <cell r="W9">
-            <v>0</v>
-          </cell>
-          <cell r="Z9">
-            <v>1.9290000000000003E-4</v>
-          </cell>
-          <cell r="AA9">
-            <v>4.4299999999999993E-5</v>
-          </cell>
-          <cell r="AB9">
-            <v>52295.464183899996</v>
-          </cell>
-          <cell r="AC9">
-            <v>5.6000000000000008E-2</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="B10">
-            <v>512</v>
-          </cell>
-          <cell r="C10">
-            <v>9.3680000000000011E-4</v>
-          </cell>
-          <cell r="D10">
-            <v>8.5400000000000016E-5</v>
-          </cell>
-          <cell r="E10">
-            <v>70083.514447100009</v>
-          </cell>
-          <cell r="F10">
-            <v>0</v>
-          </cell>
-          <cell r="I10">
-            <v>4.1780000000000002E-4</v>
-          </cell>
-          <cell r="J10">
-            <v>3.4700000000000003E-5</v>
-          </cell>
-          <cell r="K10">
-            <v>69797.020971200007</v>
-          </cell>
-          <cell r="L10">
-            <v>0.10800000000000001</v>
-          </cell>
-          <cell r="S10">
-            <v>512</v>
-          </cell>
-          <cell r="T10">
-            <v>6.4900000000000005E-4</v>
-          </cell>
-          <cell r="U10">
-            <v>8.3399999999999994E-5</v>
-          </cell>
-          <cell r="V10">
-            <v>70126.190825999991</v>
-          </cell>
-          <cell r="W10">
-            <v>0</v>
-          </cell>
-          <cell r="Z10">
-            <v>1.9689999999999999E-4</v>
-          </cell>
-          <cell r="AA10">
-            <v>3.4099999999999995E-5</v>
-          </cell>
-          <cell r="AB10">
-            <v>69766.4187676</v>
-          </cell>
-          <cell r="AC10">
-            <v>5.3000000000000005E-2</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="B11">
-            <v>640</v>
-          </cell>
-          <cell r="C11">
-            <v>1.0509E-3</v>
-          </cell>
-          <cell r="D11">
-            <v>8.6300000000000011E-5</v>
-          </cell>
-          <cell r="E11">
-            <v>87896.877479699993</v>
-          </cell>
-          <cell r="F11">
-            <v>0</v>
-          </cell>
-          <cell r="I11">
-            <v>4.103E-4</v>
-          </cell>
-          <cell r="J11">
-            <v>2.5100000000000004E-5</v>
-          </cell>
-          <cell r="K11">
-            <v>86995.931843299986</v>
-          </cell>
-          <cell r="L11">
-            <v>5.2000000000000005E-2</v>
-          </cell>
-          <cell r="S11">
-            <v>640</v>
-          </cell>
-          <cell r="T11">
-            <v>8.3900000000000001E-4</v>
-          </cell>
-          <cell r="U11">
-            <v>8.5900000000000014E-5</v>
-          </cell>
-          <cell r="V11">
-            <v>88080.382773500009</v>
-          </cell>
-          <cell r="W11">
-            <v>0</v>
-          </cell>
-          <cell r="Z11">
-            <v>2.1990000000000001E-4</v>
-          </cell>
-          <cell r="AA11">
-            <v>2.5600000000000006E-5</v>
-          </cell>
-          <cell r="AB11">
-            <v>87305.134951700005</v>
-          </cell>
-          <cell r="AC11">
-            <v>0.11899999999999999</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="B12">
-            <v>768</v>
-          </cell>
-          <cell r="C12">
-            <v>7.17309E-2</v>
-          </cell>
-          <cell r="D12">
-            <v>1.2000000000000002E-4</v>
-          </cell>
-          <cell r="E12">
-            <v>93581.590693999999</v>
-          </cell>
-          <cell r="F12">
-            <v>0</v>
-          </cell>
-          <cell r="I12">
-            <v>5.0905999999999989E-3</v>
-          </cell>
-          <cell r="J12">
-            <v>1.9699999999999999E-4</v>
-          </cell>
-          <cell r="K12">
-            <v>91091.661662600003</v>
-          </cell>
-          <cell r="L12">
-            <v>4.9999999999999996E-2</v>
-          </cell>
-          <cell r="S12">
-            <v>768</v>
-          </cell>
-          <cell r="T12">
-            <v>6.9628200000000001E-2</v>
-          </cell>
-          <cell r="U12">
-            <v>1.2000000000000002E-4</v>
-          </cell>
-          <cell r="V12">
-            <v>93563.075730600001</v>
-          </cell>
-          <cell r="W12">
-            <v>0</v>
-          </cell>
-          <cell r="Z12">
-            <v>4.9291999999999999E-3</v>
-          </cell>
-          <cell r="AA12">
-            <v>2.0130000000000001E-4</v>
-          </cell>
-          <cell r="AB12">
-            <v>91087.538745800004</v>
-          </cell>
-          <cell r="AC12">
-            <v>6.0000000000000012E-2</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="B13">
-            <v>896</v>
-          </cell>
-          <cell r="C13">
-            <v>7.6499400000000009E-2</v>
-          </cell>
-          <cell r="D13">
-            <v>1.4100000000000004E-4</v>
-          </cell>
-          <cell r="E13">
-            <v>93572.373676800009</v>
-          </cell>
-          <cell r="F13">
-            <v>0</v>
-          </cell>
-          <cell r="I13">
-            <v>5.8661999999999994E-3</v>
-          </cell>
-          <cell r="J13">
-            <v>3.9160000000000003E-4</v>
-          </cell>
-          <cell r="K13">
-            <v>92280.248612299998</v>
-          </cell>
-          <cell r="L13">
-            <v>9.9999999999999992E-2</v>
-          </cell>
-          <cell r="S13">
-            <v>896</v>
-          </cell>
-          <cell r="T13">
-            <v>7.6671800000000012E-2</v>
-          </cell>
-          <cell r="U13">
-            <v>1.4090000000000004E-4</v>
-          </cell>
-          <cell r="V13">
-            <v>93584.696719300002</v>
-          </cell>
-          <cell r="W13">
-            <v>0</v>
-          </cell>
-          <cell r="Z13">
-            <v>5.7063000000000001E-3</v>
-          </cell>
-          <cell r="AA13">
-            <v>3.9110000000000002E-4</v>
-          </cell>
-          <cell r="AB13">
-            <v>92320.009301600003</v>
-          </cell>
-          <cell r="AC13">
-            <v>4.9999999999999996E-2</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="B14">
-            <v>1024</v>
-          </cell>
-          <cell r="C14">
-            <v>7.5401599999999999E-2</v>
-          </cell>
-          <cell r="D14">
-            <v>1.6150000000000002E-4</v>
-          </cell>
-          <cell r="E14">
-            <v>93631.19045899999</v>
-          </cell>
-          <cell r="F14">
-            <v>0</v>
-          </cell>
-          <cell r="I14">
-            <v>6.5946000000000008E-3</v>
-          </cell>
-          <cell r="J14">
-            <v>5.6949999999999991E-4</v>
-          </cell>
-          <cell r="K14">
-            <v>93294.213047600002</v>
-          </cell>
-          <cell r="L14">
-            <v>4.6999999999999993E-2</v>
-          </cell>
-          <cell r="S14">
-            <v>1024</v>
-          </cell>
-          <cell r="T14">
-            <v>7.7855099999999997E-2</v>
-          </cell>
-          <cell r="U14">
-            <v>1.6160000000000002E-4</v>
-          </cell>
-          <cell r="V14">
-            <v>93629.4816096</v>
-          </cell>
-          <cell r="W14">
-            <v>0</v>
-          </cell>
-          <cell r="Z14">
-            <v>6.4381000000000004E-3</v>
-          </cell>
-          <cell r="AA14">
-            <v>5.689E-4</v>
-          </cell>
-          <cell r="AB14">
-            <v>93239.203584000003</v>
-          </cell>
-          <cell r="AC14">
-            <v>9.2999999999999985E-2</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="B15">
-            <v>1152</v>
-          </cell>
-          <cell r="C15">
-            <v>7.8402199999999991E-2</v>
-          </cell>
-          <cell r="D15">
-            <v>1.8190000000000003E-4</v>
-          </cell>
-          <cell r="E15">
-            <v>93644.150759299999</v>
-          </cell>
-          <cell r="F15">
-            <v>0</v>
-          </cell>
-          <cell r="I15">
-            <v>7.3479999999999986E-3</v>
-          </cell>
-          <cell r="J15">
-            <v>7.1880000000000002E-4</v>
-          </cell>
-          <cell r="K15">
-            <v>93997.232500200029</v>
-          </cell>
-          <cell r="L15">
-            <v>8.299999999999999E-2</v>
-          </cell>
-          <cell r="S15">
-            <v>1152</v>
-          </cell>
-          <cell r="T15">
-            <v>7.5410699999999983E-2</v>
-          </cell>
-          <cell r="U15">
-            <v>1.8220000000000001E-4</v>
-          </cell>
-          <cell r="V15">
-            <v>93652.038279800006</v>
-          </cell>
-          <cell r="W15">
-            <v>0</v>
-          </cell>
-          <cell r="Z15">
-            <v>7.2344999999999996E-3</v>
-          </cell>
-          <cell r="AA15">
-            <v>7.2959999999999995E-4</v>
-          </cell>
-          <cell r="AB15">
-            <v>94018.391845100006</v>
-          </cell>
-          <cell r="AC15">
-            <v>5.2000000000000005E-2</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="B16">
-            <v>1280</v>
-          </cell>
-          <cell r="C16">
-            <v>7.4444800000000005E-2</v>
-          </cell>
-          <cell r="D16">
-            <v>2.0259999999999999E-4</v>
-          </cell>
-          <cell r="E16">
-            <v>93654.461065800002</v>
-          </cell>
-          <cell r="F16">
-            <v>0</v>
-          </cell>
-          <cell r="I16">
-            <v>8.3416000000000011E-3</v>
-          </cell>
-          <cell r="J16">
-            <v>8.5459999999999996E-4</v>
-          </cell>
-          <cell r="K16">
-            <v>94659.673357399995</v>
-          </cell>
-          <cell r="L16">
-            <v>1.8999999999999996E-2</v>
-          </cell>
-          <cell r="S16">
-            <v>1280</v>
-          </cell>
-          <cell r="T16">
-            <v>7.4295299999999995E-2</v>
-          </cell>
-          <cell r="U16">
-            <v>2.0250000000000004E-4</v>
-          </cell>
-          <cell r="V16">
-            <v>93688.74889979999</v>
-          </cell>
-          <cell r="W16">
-            <v>0</v>
-          </cell>
-          <cell r="Z16">
-            <v>8.2635E-3</v>
-          </cell>
-          <cell r="AA16">
-            <v>8.7139999999999993E-4</v>
-          </cell>
-          <cell r="AB16">
-            <v>94569.700130700017</v>
-          </cell>
-          <cell r="AC16">
-            <v>3.7999999999999992E-2</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="B17">
-            <v>1408</v>
-          </cell>
-          <cell r="C17">
-            <v>7.5332099999999999E-2</v>
-          </cell>
-          <cell r="D17">
-            <v>2.2369999999999999E-4</v>
-          </cell>
-          <cell r="E17">
-            <v>93704.911762599993</v>
-          </cell>
-          <cell r="F17">
-            <v>0</v>
-          </cell>
-          <cell r="I17">
-            <v>9.0388000000000013E-3</v>
-          </cell>
-          <cell r="J17">
-            <v>9.9430000000000004E-4</v>
-          </cell>
-          <cell r="K17">
-            <v>95043.688907499993</v>
-          </cell>
-          <cell r="L17">
-            <v>0.217</v>
-          </cell>
-          <cell r="S17">
-            <v>1408</v>
-          </cell>
-          <cell r="T17">
-            <v>8.1909099999999999E-2</v>
-          </cell>
-          <cell r="U17">
-            <v>2.2359999999999996E-4</v>
-          </cell>
-          <cell r="V17">
-            <v>93685.618883300005</v>
-          </cell>
-          <cell r="W17">
-            <v>0</v>
-          </cell>
-          <cell r="Z17">
-            <v>8.9073999999999993E-3</v>
-          </cell>
-          <cell r="AA17">
-            <v>9.9170000000000009E-4</v>
-          </cell>
-          <cell r="AB17">
-            <v>95105.498003800021</v>
-          </cell>
-          <cell r="AC17">
-            <v>0.14499999999999996</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="B18">
-            <v>1536</v>
-          </cell>
-          <cell r="C18">
-            <v>6.8223999999999993E-2</v>
-          </cell>
-          <cell r="D18">
-            <v>2.4439999999999998E-4</v>
-          </cell>
-          <cell r="E18">
-            <v>93745.519585699978</v>
-          </cell>
-          <cell r="F18">
-            <v>0</v>
-          </cell>
-          <cell r="I18">
-            <v>7.3020000000000003E-3</v>
-          </cell>
-          <cell r="J18">
-            <v>9.1159999999999993E-4</v>
-          </cell>
-          <cell r="K18">
-            <v>91834.754220799994</v>
-          </cell>
-          <cell r="L18">
-            <v>2.9000000000000005E-2</v>
-          </cell>
-          <cell r="S18">
-            <v>1536</v>
-          </cell>
-          <cell r="T18">
-            <v>5.9132300000000006E-2</v>
-          </cell>
-          <cell r="U18">
-            <v>2.4380000000000002E-4</v>
-          </cell>
-          <cell r="V18">
-            <v>93837.239220600008</v>
-          </cell>
-          <cell r="W18">
-            <v>0</v>
-          </cell>
-          <cell r="Z18">
-            <v>7.2446000000000012E-3</v>
-          </cell>
-          <cell r="AA18">
-            <v>9.029000000000001E-4</v>
-          </cell>
-          <cell r="AB18">
-            <v>91842.884035600015</v>
-          </cell>
-          <cell r="AC18">
-            <v>3.2999999999999995E-2</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -10240,168 +9493,168 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F31A7D07-17FC-4E13-80CE-BD2BDD98C521}">
   <dimension ref="B2:AG18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="17" max="18" width="9.140625" style="2"/>
+    <col min="17" max="18" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="T2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U2" s="1"/>
-      <c r="V2" s="1"/>
-      <c r="W2" s="1"/>
-      <c r="X2" s="1"/>
-      <c r="Y2" s="1"/>
-      <c r="Z2" s="1"/>
-      <c r="AA2" s="1"/>
-      <c r="AB2" s="1"/>
-      <c r="AC2" s="1"/>
-      <c r="AD2" s="1"/>
-      <c r="AE2" s="1"/>
-      <c r="AF2" s="1"/>
-      <c r="AG2" s="1"/>
-    </row>
-    <row r="3" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="T3" s="1"/>
-      <c r="U3" s="1"/>
-      <c r="V3" s="1"/>
-      <c r="W3" s="1"/>
-      <c r="X3" s="1"/>
-      <c r="Y3" s="1"/>
-      <c r="Z3" s="1"/>
-      <c r="AA3" s="1"/>
-      <c r="AB3" s="1"/>
-      <c r="AC3" s="1"/>
-      <c r="AD3" s="1"/>
-      <c r="AE3" s="1"/>
-      <c r="AF3" s="1"/>
-      <c r="AG3" s="1"/>
-    </row>
-    <row r="5" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:33">
+      <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="T2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="2"/>
+      <c r="Z2" s="2"/>
+      <c r="AA2" s="2"/>
+      <c r="AB2" s="2"/>
+      <c r="AC2" s="2"/>
+      <c r="AD2" s="2"/>
+      <c r="AE2" s="2"/>
+      <c r="AF2" s="2"/>
+      <c r="AG2" s="2"/>
+    </row>
+    <row r="3" spans="2:33">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2"/>
+      <c r="V3" s="2"/>
+      <c r="W3" s="2"/>
+      <c r="X3" s="2"/>
+      <c r="Y3" s="2"/>
+      <c r="Z3" s="2"/>
+      <c r="AA3" s="2"/>
+      <c r="AB3" s="2"/>
+      <c r="AC3" s="2"/>
+      <c r="AD3" s="2"/>
+      <c r="AE3" s="2"/>
+      <c r="AF3" s="2"/>
+      <c r="AG3" s="2"/>
+    </row>
+    <row r="5" spans="2:33" ht="15" customHeight="1">
       <c r="B5" s="3" t="s">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="S5" s="3" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
       <c r="Y5" s="3" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="Z5" s="3"/>
       <c r="AA5" s="3"/>
       <c r="AB5" s="3"/>
       <c r="AC5" s="3"/>
     </row>
-    <row r="6" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:33">
       <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
         <v>10</v>
       </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" t="s">
-        <v>34</v>
-      </c>
       <c r="H6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" t="s">
+        <v>11</v>
+      </c>
+      <c r="J6" t="s">
+        <v>12</v>
+      </c>
+      <c r="K6" t="s">
+        <v>13</v>
+      </c>
+      <c r="L6" t="s">
+        <v>14</v>
+      </c>
+      <c r="S6" t="s">
+        <v>6</v>
+      </c>
+      <c r="T6" t="s">
+        <v>7</v>
+      </c>
+      <c r="U6" t="s">
+        <v>8</v>
+      </c>
+      <c r="V6" t="s">
+        <v>9</v>
+      </c>
+      <c r="W6" t="s">
         <v>10</v>
       </c>
-      <c r="I6" t="s">
-        <v>35</v>
-      </c>
-      <c r="J6" t="s">
-        <v>36</v>
-      </c>
-      <c r="K6" t="s">
-        <v>37</v>
-      </c>
-      <c r="L6" t="s">
-        <v>38</v>
-      </c>
-      <c r="S6" t="s">
-        <v>10</v>
-      </c>
-      <c r="T6" t="s">
-        <v>31</v>
-      </c>
-      <c r="U6" t="s">
-        <v>32</v>
-      </c>
-      <c r="V6" t="s">
-        <v>33</v>
-      </c>
-      <c r="W6" t="s">
-        <v>34</v>
-      </c>
       <c r="Y6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z6" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="AA6" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="AB6" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="AC6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="2:33" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="2:33">
       <c r="B7">
         <v>128</v>
       </c>
@@ -10463,7 +9716,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="8" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:33">
       <c r="B8">
         <v>256</v>
       </c>
@@ -10525,7 +9778,7 @@
         <v>6.0000000000000012E-2</v>
       </c>
     </row>
-    <row r="9" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:33">
       <c r="B9">
         <v>384</v>
       </c>
@@ -10587,7 +9840,7 @@
         <v>7.1000000000000008E-2</v>
       </c>
     </row>
-    <row r="10" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:33">
       <c r="B10">
         <v>512</v>
       </c>
@@ -10649,7 +9902,7 @@
         <v>6.4000000000000015E-2</v>
       </c>
     </row>
-    <row r="11" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:33">
       <c r="B11">
         <v>640</v>
       </c>
@@ -10711,7 +9964,7 @@
         <v>0.10300000000000001</v>
       </c>
     </row>
-    <row r="12" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:33">
       <c r="B12">
         <v>768</v>
       </c>
@@ -10773,7 +10026,7 @@
         <v>5.6000000000000008E-2</v>
       </c>
     </row>
-    <row r="13" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:33">
       <c r="B13">
         <v>896</v>
       </c>
@@ -10835,7 +10088,7 @@
         <v>5.9000000000000011E-2</v>
       </c>
     </row>
-    <row r="14" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:33">
       <c r="B14">
         <v>1024</v>
       </c>
@@ -10897,7 +10150,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="15" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:33">
       <c r="B15">
         <v>1152</v>
       </c>
@@ -10959,7 +10212,7 @@
         <v>3.9999999999999994E-2</v>
       </c>
     </row>
-    <row r="16" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:33">
       <c r="B16">
         <v>1280</v>
       </c>
@@ -11021,7 +10274,7 @@
         <v>8.199999999999999E-2</v>
       </c>
     </row>
-    <row r="17" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:29">
       <c r="B17">
         <v>1408</v>
       </c>
@@ -11083,7 +10336,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="18" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:29">
       <c r="B18">
         <v>1536</v>
       </c>
@@ -11162,82 +10415,82 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:Z89"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>22</v>
+      </c>
+      <c r="R3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S3" t="s">
+        <v>24</v>
+      </c>
+      <c r="V3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" t="s">
-        <v>9</v>
-      </c>
-      <c r="L3" t="s">
-        <v>2</v>
-      </c>
-      <c r="M3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P3" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>7</v>
-      </c>
-      <c r="R3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S3" t="s">
-        <v>9</v>
-      </c>
-      <c r="V3" t="s">
-        <v>10</v>
-      </c>
       <c r="W3" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="X3" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="Y3" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="Z3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26">
       <c r="A4">
         <v>1</v>
       </c>
@@ -11306,7 +10559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26">
       <c r="A5">
         <v>5</v>
       </c>
@@ -11375,7 +10628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26">
       <c r="A6">
         <v>2</v>
       </c>
@@ -11444,7 +10697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26">
       <c r="A7">
         <v>6</v>
       </c>
@@ -11513,7 +10766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26">
       <c r="A8">
         <v>4</v>
       </c>
@@ -11582,7 +10835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26">
       <c r="A9">
         <v>3</v>
       </c>
@@ -11651,7 +10904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26">
       <c r="A10">
         <v>7</v>
       </c>
@@ -11720,7 +10973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26">
       <c r="A11">
         <v>8</v>
       </c>
@@ -11789,7 +11042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26">
       <c r="A12">
         <v>9</v>
       </c>
@@ -11858,7 +11111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26">
       <c r="A13">
         <v>10</v>
       </c>
@@ -11927,9 +11180,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B14">
         <f t="shared" ref="B14:H14" si="0">AVERAGE(B4:B13)</f>
@@ -11960,7 +11213,7 @@
         <v>16851.870264599998</v>
       </c>
       <c r="L14" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M14">
         <f t="shared" ref="M14:S14" si="1">AVERAGE(M4:M13)</f>
@@ -12010,7 +11263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26">
       <c r="V15">
         <v>1536</v>
       </c>
@@ -12031,65 +11284,65 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="L17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
       <c r="A18" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D18" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F18" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G18" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H18" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L18" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M18" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N18" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O18" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P18" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q18" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R18" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
       <c r="A19">
         <v>1</v>
       </c>
@@ -12139,7 +11392,7 @@
         <v>11436.077332000001</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19">
       <c r="A20">
         <v>6</v>
       </c>
@@ -12189,7 +11442,7 @@
         <v>11436.561868999999</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19">
       <c r="A21">
         <v>3</v>
       </c>
@@ -12239,7 +11492,7 @@
         <v>11420.893117</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19">
       <c r="A22">
         <v>5</v>
       </c>
@@ -12289,7 +11542,7 @@
         <v>11419.139526999999</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19">
       <c r="A23">
         <v>2</v>
       </c>
@@ -12339,7 +11592,7 @@
         <v>11429.924198000001</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19">
       <c r="A24">
         <v>4</v>
       </c>
@@ -12389,7 +11642,7 @@
         <v>11439.593069</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19">
       <c r="A25">
         <v>7</v>
       </c>
@@ -12439,7 +11692,7 @@
         <v>11425.439856000001</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19">
       <c r="A26">
         <v>8</v>
       </c>
@@ -12489,7 +11742,7 @@
         <v>11415.53102</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19">
       <c r="A27">
         <v>9</v>
       </c>
@@ -12539,7 +11792,7 @@
         <v>11408.035787000001</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19">
       <c r="A28">
         <v>10</v>
       </c>
@@ -12589,9 +11842,9 @@
         <v>11414.924872</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19">
       <c r="A29" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B29">
         <f t="shared" ref="B29:H29" si="2">AVERAGE(B19:B28)</f>
@@ -12622,7 +11875,7 @@
         <v>17000.609294000002</v>
       </c>
       <c r="L29" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M29">
         <f t="shared" ref="M29:S29" si="3">AVERAGE(M19:M28)</f>
@@ -12653,65 +11906,65 @@
         <v>11424.612064699999</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19">
       <c r="A32" t="s">
+        <v>31</v>
+      </c>
+      <c r="L32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19">
+      <c r="A33" t="s">
         <v>17</v>
       </c>
-      <c r="L32" t="s">
+      <c r="B33" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>2</v>
-      </c>
-      <c r="B33" t="s">
-        <v>3</v>
-      </c>
       <c r="C33" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D33" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E33" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F33" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G33" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H33" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L33" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M33" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N33" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O33" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P33" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q33" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R33" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S33" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19">
       <c r="A34">
         <v>1</v>
       </c>
@@ -12761,7 +12014,7 @@
         <v>10179.982737</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19">
       <c r="A35">
         <v>2</v>
       </c>
@@ -12811,7 +12064,7 @@
         <v>10171.936787000001</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19">
       <c r="A36">
         <v>4</v>
       </c>
@@ -12861,7 +12114,7 @@
         <v>10156.811867</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19">
       <c r="A37">
         <v>5</v>
       </c>
@@ -12911,7 +12164,7 @@
         <v>10152.769667</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19">
       <c r="A38">
         <v>6</v>
       </c>
@@ -12961,7 +12214,7 @@
         <v>10148.347632000001</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19">
       <c r="A39">
         <v>3</v>
       </c>
@@ -13011,7 +12264,7 @@
         <v>10154.259007000001</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19">
       <c r="A40">
         <v>8</v>
       </c>
@@ -13061,7 +12314,7 @@
         <v>10152.843091999999</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19">
       <c r="A41">
         <v>7</v>
       </c>
@@ -13111,7 +12364,7 @@
         <v>10173.248240999999</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19">
       <c r="A42">
         <v>9</v>
       </c>
@@ -13161,7 +12414,7 @@
         <v>10185.688731</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19">
       <c r="A43">
         <v>10</v>
       </c>
@@ -13211,9 +12464,9 @@
         <v>10182.632766000001</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19">
       <c r="A44" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B44">
         <f t="shared" ref="B44:H44" si="4">AVERAGE(B34:B43)</f>
@@ -13244,7 +12497,7 @@
         <v>17141.551112699999</v>
       </c>
       <c r="L44" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M44">
         <f t="shared" ref="M44:S44" si="5">AVERAGE(M34:M43)</f>
@@ -13275,65 +12528,65 @@
         <v>10165.852052699998</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19">
       <c r="A47" t="s">
+        <v>33</v>
+      </c>
+      <c r="L47" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19">
+      <c r="A48" t="s">
+        <v>17</v>
+      </c>
+      <c r="B48" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" t="s">
         <v>19</v>
       </c>
-      <c r="L47" t="s">
+      <c r="D48" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>2</v>
-      </c>
-      <c r="B48" t="s">
-        <v>3</v>
-      </c>
-      <c r="C48" t="s">
-        <v>4</v>
-      </c>
-      <c r="D48" t="s">
-        <v>5</v>
-      </c>
       <c r="E48" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F48" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G48" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H48" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L48" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M48" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N48" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O48" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P48" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q48" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R48" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S48" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19">
       <c r="A49">
         <v>4</v>
       </c>
@@ -13383,7 +12636,7 @@
         <v>9167.1614430000009</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19">
       <c r="A50">
         <v>5</v>
       </c>
@@ -13433,7 +12686,7 @@
         <v>9169.5692400000007</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19">
       <c r="A51">
         <v>1</v>
       </c>
@@ -13483,7 +12736,7 @@
         <v>9141.1862839999994</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19">
       <c r="A52">
         <v>3</v>
       </c>
@@ -13533,7 +12786,7 @@
         <v>9163.3031090000004</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19">
       <c r="A53">
         <v>2</v>
       </c>
@@ -13583,7 +12836,7 @@
         <v>9140.9543790000007</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19">
       <c r="A54">
         <v>6</v>
       </c>
@@ -13633,7 +12886,7 @@
         <v>9134.8426070000005</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19">
       <c r="A55">
         <v>8</v>
       </c>
@@ -13683,7 +12936,7 @@
         <v>9137.5864130000009</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19">
       <c r="A56">
         <v>9</v>
       </c>
@@ -13733,7 +12986,7 @@
         <v>9136.2706039999994</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19">
       <c r="A57">
         <v>7</v>
       </c>
@@ -13783,7 +13036,7 @@
         <v>9139.5687330000001</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19">
       <c r="A58">
         <v>10</v>
       </c>
@@ -13833,9 +13086,9 @@
         <v>9147.5755520000002</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19">
       <c r="A59" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B59">
         <f t="shared" ref="B59:H59" si="6">AVERAGE(B49:B58)</f>
@@ -13866,7 +13119,7 @@
         <v>17141.018029699997</v>
       </c>
       <c r="L59" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M59">
         <f t="shared" ref="M59:S59" si="7">AVERAGE(M49:M58)</f>
@@ -13897,65 +13150,65 @@
         <v>9147.8018363999981</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19">
       <c r="A62" t="s">
+        <v>35</v>
+      </c>
+      <c r="L62" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19">
+      <c r="A63" t="s">
+        <v>17</v>
+      </c>
+      <c r="B63" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" t="s">
+        <v>19</v>
+      </c>
+      <c r="D63" t="s">
+        <v>20</v>
+      </c>
+      <c r="E63" t="s">
         <v>21</v>
       </c>
-      <c r="L62" t="s">
+      <c r="F63" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>2</v>
-      </c>
-      <c r="B63" t="s">
-        <v>3</v>
-      </c>
-      <c r="C63" t="s">
-        <v>4</v>
-      </c>
-      <c r="D63" t="s">
-        <v>5</v>
-      </c>
-      <c r="E63" t="s">
-        <v>6</v>
-      </c>
-      <c r="F63" t="s">
-        <v>7</v>
-      </c>
       <c r="G63" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H63" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L63" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M63" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N63" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O63" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P63" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q63" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R63" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S63" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19">
       <c r="A64">
         <v>2</v>
       </c>
@@ -14005,7 +13258,7 @@
         <v>8348.6207259999992</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19">
       <c r="A65">
         <v>5</v>
       </c>
@@ -14055,7 +13308,7 @@
         <v>8344.2257969999991</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19">
       <c r="A66">
         <v>4</v>
       </c>
@@ -14105,7 +13358,7 @@
         <v>8313.9844630000007</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19">
       <c r="A67">
         <v>1</v>
       </c>
@@ -14155,7 +13408,7 @@
         <v>8308.9333110000007</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19">
       <c r="A68">
         <v>3</v>
       </c>
@@ -14205,7 +13458,7 @@
         <v>8373.6063880000002</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19">
       <c r="A69">
         <v>6</v>
       </c>
@@ -14255,7 +13508,7 @@
         <v>8309.0600990000003</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19">
       <c r="A70">
         <v>8</v>
       </c>
@@ -14305,7 +13558,7 @@
         <v>8306.7762380000004</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19">
       <c r="A71">
         <v>7</v>
       </c>
@@ -14355,7 +13608,7 @@
         <v>8308.6411700000008</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19">
       <c r="A72">
         <v>9</v>
       </c>
@@ -14405,7 +13658,7 @@
         <v>8306.1233960000009</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19">
       <c r="A73">
         <v>10</v>
       </c>
@@ -14455,9 +13708,9 @@
         <v>8323.6997439999996</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19">
       <c r="A74" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B74">
         <f t="shared" ref="B74:H74" si="8">AVERAGE(B64:B73)</f>
@@ -14488,7 +13741,7 @@
         <v>17202.070998300002</v>
       </c>
       <c r="L74" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M74">
         <f t="shared" ref="M74:S74" si="9">AVERAGE(M64:M73)</f>
@@ -14519,65 +13772,65 @@
         <v>8324.3671331999994</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19">
       <c r="A77" t="s">
+        <v>37</v>
+      </c>
+      <c r="L77" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19">
+      <c r="A78" t="s">
+        <v>17</v>
+      </c>
+      <c r="B78" t="s">
+        <v>18</v>
+      </c>
+      <c r="C78" t="s">
+        <v>19</v>
+      </c>
+      <c r="D78" t="s">
+        <v>20</v>
+      </c>
+      <c r="E78" t="s">
+        <v>21</v>
+      </c>
+      <c r="F78" t="s">
+        <v>22</v>
+      </c>
+      <c r="G78" t="s">
         <v>23</v>
       </c>
-      <c r="L77" t="s">
+      <c r="H78" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>2</v>
-      </c>
-      <c r="B78" t="s">
-        <v>3</v>
-      </c>
-      <c r="C78" t="s">
-        <v>4</v>
-      </c>
-      <c r="D78" t="s">
-        <v>5</v>
-      </c>
-      <c r="E78" t="s">
-        <v>6</v>
-      </c>
-      <c r="F78" t="s">
-        <v>7</v>
-      </c>
-      <c r="G78" t="s">
-        <v>8</v>
-      </c>
-      <c r="H78" t="s">
-        <v>9</v>
-      </c>
       <c r="L78" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M78" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N78" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O78" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P78" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q78" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R78" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S78" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19">
       <c r="A79">
         <v>1</v>
       </c>
@@ -14627,7 +13880,7 @@
         <v>7657.3875550000002</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19">
       <c r="A80">
         <v>5</v>
       </c>
@@ -14677,7 +13930,7 @@
         <v>7655.5000220000002</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:19">
       <c r="A81">
         <v>3</v>
       </c>
@@ -14727,7 +13980,7 @@
         <v>7636.4057590000002</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:19">
       <c r="A82">
         <v>4</v>
       </c>
@@ -14777,7 +14030,7 @@
         <v>7625.9929490000004</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:19">
       <c r="A83">
         <v>2</v>
       </c>
@@ -14827,7 +14080,7 @@
         <v>7613.8753399999996</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:19">
       <c r="A84">
         <v>8</v>
       </c>
@@ -14877,7 +14130,7 @@
         <v>7623.3386179999998</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:19">
       <c r="A85">
         <v>6</v>
       </c>
@@ -14927,7 +14180,7 @@
         <v>7605.7639509999999</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:19">
       <c r="A86">
         <v>10</v>
       </c>
@@ -14977,7 +14230,7 @@
         <v>7606.190861</v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:19">
       <c r="A87">
         <v>7</v>
       </c>
@@ -15027,7 +14280,7 @@
         <v>7621.702714</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:19">
       <c r="A88">
         <v>9</v>
       </c>
@@ -15077,9 +14330,9 @@
         <v>7660.7077300000001</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:19">
       <c r="A89" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B89">
         <f t="shared" ref="B89:H89" si="10">AVERAGE(B79:B88)</f>
@@ -15110,7 +14363,7 @@
         <v>15230.1051599</v>
       </c>
       <c r="L89" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M89">
         <f t="shared" ref="M89:S89" si="11">AVERAGE(M79:M88)</f>
@@ -15149,82 +14402,82 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:Z89"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>22</v>
+      </c>
+      <c r="R3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S3" t="s">
+        <v>24</v>
+      </c>
+      <c r="V3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" t="s">
-        <v>9</v>
-      </c>
-      <c r="L3" t="s">
-        <v>2</v>
-      </c>
-      <c r="M3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P3" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>7</v>
-      </c>
-      <c r="R3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S3" t="s">
-        <v>9</v>
-      </c>
-      <c r="V3" t="s">
-        <v>10</v>
-      </c>
       <c r="W3" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="X3" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="Y3" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="Z3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26">
       <c r="A4">
         <v>4</v>
       </c>
@@ -15293,7 +14546,7 @@
         <v>0.10699999999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26">
       <c r="A5">
         <v>7</v>
       </c>
@@ -15362,7 +14615,7 @@
         <v>5.7000000000000009E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26">
       <c r="A6">
         <v>6</v>
       </c>
@@ -15431,7 +14684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26">
       <c r="A7">
         <v>8</v>
       </c>
@@ -15500,7 +14753,7 @@
         <v>6.0000000000000012E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26">
       <c r="A8">
         <v>1</v>
       </c>
@@ -15569,7 +14822,7 @@
         <v>5.7000000000000009E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26">
       <c r="A9">
         <v>5</v>
       </c>
@@ -15638,7 +14891,7 @@
         <v>0.11000000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26">
       <c r="A10">
         <v>10</v>
       </c>
@@ -15707,7 +14960,7 @@
         <v>5.1000000000000004E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26">
       <c r="A11">
         <v>3</v>
       </c>
@@ -15776,7 +15029,7 @@
         <v>5.7000000000000009E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26">
       <c r="A12">
         <v>2</v>
       </c>
@@ -15845,7 +15098,7 @@
         <v>9.3999999999999986E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26">
       <c r="A13">
         <v>9</v>
       </c>
@@ -15914,9 +15167,9 @@
         <v>9.6999999999999989E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B14">
         <f t="shared" ref="B14:H14" si="0">AVERAGE(B4:B13)</f>
@@ -15947,7 +15200,7 @@
         <v>17026.6704274</v>
       </c>
       <c r="L14" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M14">
         <f t="shared" ref="M14:S14" si="1">AVERAGE(M4:M13)</f>
@@ -15997,7 +15250,7 @@
         <v>0.63500000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26">
       <c r="V15">
         <v>1536</v>
       </c>
@@ -16018,65 +15271,65 @@
         <v>7.3999999999999996E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="L17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
       <c r="A18" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D18" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F18" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G18" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H18" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L18" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M18" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N18" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O18" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P18" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q18" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R18" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
       <c r="A19">
         <v>1</v>
       </c>
@@ -16126,7 +15379,7 @@
         <v>11407.544581</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19">
       <c r="A20">
         <v>2</v>
       </c>
@@ -16176,7 +15429,7 @@
         <v>11407.074365</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19">
       <c r="A21">
         <v>3</v>
       </c>
@@ -16226,7 +15479,7 @@
         <v>11380.952842999999</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19">
       <c r="A22">
         <v>7</v>
       </c>
@@ -16276,7 +15529,7 @@
         <v>11380.96702</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19">
       <c r="A23">
         <v>5</v>
       </c>
@@ -16326,7 +15579,7 @@
         <v>11380.946018000001</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19">
       <c r="A24">
         <v>4</v>
       </c>
@@ -16376,7 +15629,7 @@
         <v>11380.258952</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19">
       <c r="A25">
         <v>6</v>
       </c>
@@ -16426,7 +15679,7 @@
         <v>11380.252565999999</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19">
       <c r="A26">
         <v>9</v>
       </c>
@@ -16476,7 +15729,7 @@
         <v>11379.705298999999</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19">
       <c r="A27">
         <v>10</v>
       </c>
@@ -16526,7 +15779,7 @@
         <v>11379.510902</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19">
       <c r="A28">
         <v>8</v>
       </c>
@@ -16576,9 +15829,9 @@
         <v>11380.96499</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19">
       <c r="A29" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B29">
         <f t="shared" ref="B29:H29" si="2">AVERAGE(B19:B28)</f>
@@ -16609,7 +15862,7 @@
         <v>17048.417589099998</v>
       </c>
       <c r="L29" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M29">
         <f t="shared" ref="M29:S29" si="3">AVERAGE(M19:M28)</f>
@@ -16640,65 +15893,65 @@
         <v>11385.8177536</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19">
       <c r="A32" t="s">
+        <v>31</v>
+      </c>
+      <c r="L32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19">
+      <c r="A33" t="s">
         <v>17</v>
       </c>
-      <c r="L32" t="s">
+      <c r="B33" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>2</v>
-      </c>
-      <c r="B33" t="s">
-        <v>3</v>
-      </c>
       <c r="C33" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D33" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E33" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F33" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G33" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H33" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L33" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M33" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N33" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O33" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P33" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q33" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R33" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S33" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19">
       <c r="A34">
         <v>1</v>
       </c>
@@ -16748,7 +16001,7 @@
         <v>10230.013695</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19">
       <c r="A35">
         <v>5</v>
       </c>
@@ -16798,7 +16051,7 @@
         <v>10227.564152000001</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19">
       <c r="A36">
         <v>9</v>
       </c>
@@ -16848,7 +16101,7 @@
         <v>10189.125404</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19">
       <c r="A37">
         <v>3</v>
       </c>
@@ -16898,7 +16151,7 @@
         <v>10188.174079</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19">
       <c r="A38">
         <v>7</v>
       </c>
@@ -16948,7 +16201,7 @@
         <v>10187.640713999999</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19">
       <c r="A39">
         <v>6</v>
       </c>
@@ -16998,7 +16251,7 @@
         <v>10187.215699</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19">
       <c r="A40">
         <v>2</v>
       </c>
@@ -17048,7 +16301,7 @@
         <v>10187.465679999999</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19">
       <c r="A41">
         <v>4</v>
       </c>
@@ -17098,7 +16351,7 @@
         <v>10186.798623000001</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19">
       <c r="A42">
         <v>10</v>
       </c>
@@ -17148,7 +16401,7 @@
         <v>10188.188274</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19">
       <c r="A43">
         <v>8</v>
       </c>
@@ -17198,9 +16451,9 @@
         <v>10187.099007000001</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19">
       <c r="A44" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B44">
         <f t="shared" ref="B44:H44" si="4">AVERAGE(B34:B43)</f>
@@ -17231,7 +16484,7 @@
         <v>17039.1948376</v>
       </c>
       <c r="L44" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M44">
         <f t="shared" ref="M44:S44" si="5">AVERAGE(M34:M43)</f>
@@ -17262,65 +16515,65 @@
         <v>10195.9285327</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19">
       <c r="A47" t="s">
+        <v>33</v>
+      </c>
+      <c r="L47" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19">
+      <c r="A48" t="s">
+        <v>17</v>
+      </c>
+      <c r="B48" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" t="s">
         <v>19</v>
       </c>
-      <c r="L47" t="s">
+      <c r="D48" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>2</v>
-      </c>
-      <c r="B48" t="s">
-        <v>3</v>
-      </c>
-      <c r="C48" t="s">
-        <v>4</v>
-      </c>
-      <c r="D48" t="s">
-        <v>5</v>
-      </c>
       <c r="E48" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F48" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G48" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H48" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L48" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M48" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N48" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O48" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P48" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q48" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R48" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S48" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19">
       <c r="A49">
         <v>1</v>
       </c>
@@ -17370,7 +16623,7 @@
         <v>9279.5646059999999</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19">
       <c r="A50">
         <v>4</v>
       </c>
@@ -17420,7 +16673,7 @@
         <v>9277.9226820000003</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19">
       <c r="A51">
         <v>10</v>
       </c>
@@ -17470,7 +16723,7 @@
         <v>9227.1061809999992</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19">
       <c r="A52">
         <v>6</v>
       </c>
@@ -17520,7 +16773,7 @@
         <v>9224.9168809999992</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19">
       <c r="A53">
         <v>3</v>
       </c>
@@ -17570,7 +16823,7 @@
         <v>9225.0664359999992</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19">
       <c r="A54">
         <v>8</v>
       </c>
@@ -17620,7 +16873,7 @@
         <v>9224.1887299999999</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19">
       <c r="A55">
         <v>5</v>
       </c>
@@ -17670,7 +16923,7 @@
         <v>9226.1584700000003</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19">
       <c r="A56">
         <v>9</v>
       </c>
@@ -17720,7 +16973,7 @@
         <v>9225.6325859999997</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19">
       <c r="A57">
         <v>2</v>
       </c>
@@ -17770,7 +17023,7 @@
         <v>9226.9758899999997</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19">
       <c r="A58">
         <v>7</v>
       </c>
@@ -17820,9 +17073,9 @@
         <v>9224.8545300000005</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19">
       <c r="A59" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B59">
         <f t="shared" ref="B59:H59" si="6">AVERAGE(B49:B58)</f>
@@ -17853,7 +17106,7 @@
         <v>17064.472270499995</v>
       </c>
       <c r="L59" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M59">
         <f t="shared" ref="M59:S59" si="7">AVERAGE(M49:M58)</f>
@@ -17884,65 +17137,65 @@
         <v>9236.2386991999992</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19">
       <c r="A62" t="s">
+        <v>35</v>
+      </c>
+      <c r="L62" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19">
+      <c r="A63" t="s">
+        <v>17</v>
+      </c>
+      <c r="B63" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" t="s">
+        <v>19</v>
+      </c>
+      <c r="D63" t="s">
+        <v>20</v>
+      </c>
+      <c r="E63" t="s">
         <v>21</v>
       </c>
-      <c r="L62" t="s">
+      <c r="F63" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>2</v>
-      </c>
-      <c r="B63" t="s">
-        <v>3</v>
-      </c>
-      <c r="C63" t="s">
-        <v>4</v>
-      </c>
-      <c r="D63" t="s">
-        <v>5</v>
-      </c>
-      <c r="E63" t="s">
-        <v>6</v>
-      </c>
-      <c r="F63" t="s">
-        <v>7</v>
-      </c>
       <c r="G63" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H63" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L63" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M63" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N63" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O63" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P63" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q63" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R63" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S63" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19">
       <c r="A64">
         <v>6</v>
       </c>
@@ -17992,7 +17245,7 @@
         <v>8485.0533039999991</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19">
       <c r="A65">
         <v>7</v>
       </c>
@@ -18042,7 +17295,7 @@
         <v>8483.9067799999993</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19">
       <c r="A66">
         <v>5</v>
       </c>
@@ -18092,7 +17345,7 @@
         <v>8430.5443990000003</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19">
       <c r="A67">
         <v>8</v>
       </c>
@@ -18142,7 +17395,7 @@
         <v>8430.7505540000002</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19">
       <c r="A68">
         <v>10</v>
       </c>
@@ -18192,7 +17445,7 @@
         <v>8430.5382470000004</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19">
       <c r="A69">
         <v>2</v>
       </c>
@@ -18242,7 +17495,7 @@
         <v>8430.6071350000002</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19">
       <c r="A70">
         <v>4</v>
       </c>
@@ -18292,7 +17545,7 @@
         <v>8430.7468019999997</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19">
       <c r="A71">
         <v>1</v>
       </c>
@@ -18342,7 +17595,7 @@
         <v>8430.0300810000008</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19">
       <c r="A72">
         <v>9</v>
       </c>
@@ -18392,7 +17645,7 @@
         <v>8429.485036</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19">
       <c r="A73">
         <v>3</v>
       </c>
@@ -18442,9 +17695,9 @@
         <v>8430.4091210000006</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19">
       <c r="A74" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B74">
         <f t="shared" ref="B74:H74" si="8">AVERAGE(B64:B73)</f>
@@ -18475,7 +17728,7 @@
         <v>17045.227410500003</v>
       </c>
       <c r="L74" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M74">
         <f t="shared" ref="M74:S74" si="9">AVERAGE(M64:M73)</f>
@@ -18506,65 +17759,65 @@
         <v>8441.2071458999999</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19">
       <c r="A77" t="s">
+        <v>37</v>
+      </c>
+      <c r="L77" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19">
+      <c r="A78" t="s">
+        <v>17</v>
+      </c>
+      <c r="B78" t="s">
+        <v>18</v>
+      </c>
+      <c r="C78" t="s">
+        <v>19</v>
+      </c>
+      <c r="D78" t="s">
+        <v>20</v>
+      </c>
+      <c r="E78" t="s">
+        <v>21</v>
+      </c>
+      <c r="F78" t="s">
+        <v>22</v>
+      </c>
+      <c r="G78" t="s">
         <v>23</v>
       </c>
-      <c r="L77" t="s">
+      <c r="H78" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>2</v>
-      </c>
-      <c r="B78" t="s">
-        <v>3</v>
-      </c>
-      <c r="C78" t="s">
-        <v>4</v>
-      </c>
-      <c r="D78" t="s">
-        <v>5</v>
-      </c>
-      <c r="E78" t="s">
-        <v>6</v>
-      </c>
-      <c r="F78" t="s">
-        <v>7</v>
-      </c>
-      <c r="G78" t="s">
-        <v>8</v>
-      </c>
-      <c r="H78" t="s">
-        <v>9</v>
-      </c>
       <c r="L78" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M78" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N78" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O78" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P78" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q78" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R78" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S78" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19">
       <c r="A79">
         <v>1</v>
       </c>
@@ -18614,7 +17867,7 @@
         <v>7532.0521150000004</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19">
       <c r="A80">
         <v>5</v>
       </c>
@@ -18664,7 +17917,7 @@
         <v>7529.2562900000003</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:19">
       <c r="A81">
         <v>2</v>
       </c>
@@ -18714,7 +17967,7 @@
         <v>7455.5740850000002</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:19">
       <c r="A82">
         <v>6</v>
       </c>
@@ -18764,7 +18017,7 @@
         <v>7455.021076</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:19">
       <c r="A83">
         <v>9</v>
       </c>
@@ -18814,7 +18067,7 @@
         <v>7455.4719050000003</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:19">
       <c r="A84">
         <v>7</v>
       </c>
@@ -18864,7 +18117,7 @@
         <v>7454.2387710000003</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:19">
       <c r="A85">
         <v>4</v>
       </c>
@@ -18914,7 +18167,7 @@
         <v>7453.9421590000002</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:19">
       <c r="A86">
         <v>8</v>
       </c>
@@ -18964,7 +18217,7 @@
         <v>7454.0444710000002</v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:19">
       <c r="A87">
         <v>10</v>
       </c>
@@ -19014,7 +18267,7 @@
         <v>7455.6467240000002</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:19">
       <c r="A88">
         <v>3</v>
       </c>
@@ -19064,9 +18317,9 @@
         <v>7454.9069749999999</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:19">
       <c r="A89" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B89">
         <f t="shared" ref="B89:H89" si="10">AVERAGE(B79:B88)</f>
@@ -19097,7 +18350,7 @@
         <v>14819.055025799997</v>
       </c>
       <c r="L89" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M89">
         <f t="shared" ref="M89:S89" si="11">AVERAGE(M79:M88)</f>
@@ -19136,82 +18389,82 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A2:Z89"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>22</v>
+      </c>
+      <c r="R3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S3" t="s">
+        <v>24</v>
+      </c>
+      <c r="V3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" t="s">
-        <v>9</v>
-      </c>
-      <c r="L3" t="s">
-        <v>2</v>
-      </c>
-      <c r="M3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P3" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>7</v>
-      </c>
-      <c r="R3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S3" t="s">
-        <v>9</v>
-      </c>
-      <c r="V3" t="s">
-        <v>10</v>
-      </c>
       <c r="W3" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="X3" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="Y3" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="Z3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26">
       <c r="A4">
         <v>2</v>
       </c>
@@ -19280,7 +18533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26">
       <c r="A5">
         <v>5</v>
       </c>
@@ -19349,7 +18602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26">
       <c r="A6">
         <v>1</v>
       </c>
@@ -19418,7 +18671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26">
       <c r="A7">
         <v>4</v>
       </c>
@@ -19487,7 +18740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26">
       <c r="A8">
         <v>3</v>
       </c>
@@ -19556,7 +18809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26">
       <c r="A9">
         <v>7</v>
       </c>
@@ -19625,7 +18878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26">
       <c r="A10">
         <v>8</v>
       </c>
@@ -19694,7 +18947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26">
       <c r="A11">
         <v>9</v>
       </c>
@@ -19763,7 +19016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26">
       <c r="A12">
         <v>10</v>
       </c>
@@ -19832,7 +19085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26">
       <c r="A13">
         <v>6</v>
       </c>
@@ -19901,9 +19154,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B14">
         <f t="shared" ref="B14:H14" si="0">AVERAGE(B4:B13)</f>
@@ -19934,7 +19187,7 @@
         <v>16880.342212399999</v>
       </c>
       <c r="L14" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M14">
         <f t="shared" ref="M14:S14" si="1">AVERAGE(M4:M13)</f>
@@ -19984,7 +19237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26">
       <c r="V15">
         <v>1536</v>
       </c>
@@ -20005,65 +19258,65 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="L17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
       <c r="A18" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D18" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F18" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G18" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H18" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L18" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M18" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N18" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O18" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P18" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q18" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R18" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
       <c r="A19">
         <v>1</v>
       </c>
@@ -20113,7 +19366,7 @@
         <v>11438.67734</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19">
       <c r="A20">
         <v>5</v>
       </c>
@@ -20163,7 +19416,7 @@
         <v>11437.654248999999</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19">
       <c r="A21">
         <v>4</v>
       </c>
@@ -20213,7 +19466,7 @@
         <v>11419.382506</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19">
       <c r="A22">
         <v>2</v>
       </c>
@@ -20263,7 +19516,7 @@
         <v>11435.838197999999</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19">
       <c r="A23">
         <v>7</v>
       </c>
@@ -20313,7 +19566,7 @@
         <v>11429.864384</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19">
       <c r="A24">
         <v>3</v>
       </c>
@@ -20363,7 +19616,7 @@
         <v>11444.217661999999</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19">
       <c r="A25">
         <v>6</v>
       </c>
@@ -20413,7 +19666,7 @@
         <v>11424.664707</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19">
       <c r="A26">
         <v>8</v>
       </c>
@@ -20463,7 +19716,7 @@
         <v>11415.349875</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19">
       <c r="A27">
         <v>9</v>
       </c>
@@ -20513,7 +19766,7 @@
         <v>11420.625964000001</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19">
       <c r="A28">
         <v>10</v>
       </c>
@@ -20563,9 +19816,9 @@
         <v>11436.507133999999</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19">
       <c r="A29" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B29">
         <f t="shared" ref="B29:H29" si="2">AVERAGE(B19:B28)</f>
@@ -20596,7 +19849,7 @@
         <v>16964.179917900001</v>
       </c>
       <c r="L29" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M29">
         <f t="shared" ref="M29:S29" si="3">AVERAGE(M19:M28)</f>
@@ -20627,65 +19880,65 @@
         <v>11430.278201900001</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19">
       <c r="A32" t="s">
+        <v>31</v>
+      </c>
+      <c r="L32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19">
+      <c r="A33" t="s">
         <v>17</v>
       </c>
-      <c r="L32" t="s">
+      <c r="B33" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>2</v>
-      </c>
-      <c r="B33" t="s">
-        <v>3</v>
-      </c>
       <c r="C33" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D33" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E33" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F33" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G33" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H33" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L33" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M33" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N33" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O33" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P33" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q33" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R33" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S33" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19">
       <c r="A34">
         <v>1</v>
       </c>
@@ -20735,7 +19988,7 @@
         <v>11298.173643</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19">
       <c r="A35">
         <v>4</v>
       </c>
@@ -20785,7 +20038,7 @@
         <v>5691.5054</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19">
       <c r="A36">
         <v>5</v>
       </c>
@@ -20835,7 +20088,7 @@
         <v>11279.192718</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19">
       <c r="A37">
         <v>3</v>
       </c>
@@ -20885,7 +20138,7 @@
         <v>11276.816790000001</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19">
       <c r="A38">
         <v>2</v>
       </c>
@@ -20935,7 +20188,7 @@
         <v>11287.077273999999</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19">
       <c r="A39">
         <v>6</v>
       </c>
@@ -20985,7 +20238,7 @@
         <v>5665.2243820000003</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19">
       <c r="A40">
         <v>9</v>
       </c>
@@ -21035,7 +20288,7 @@
         <v>11279.603885</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19">
       <c r="A41">
         <v>7</v>
       </c>
@@ -21085,7 +20338,7 @@
         <v>11279.902988</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19">
       <c r="A42">
         <v>10</v>
       </c>
@@ -21135,7 +20388,7 @@
         <v>11304.388553999999</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19">
       <c r="A43">
         <v>8</v>
       </c>
@@ -21185,9 +20438,9 @@
         <v>11289.53017</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19">
       <c r="A44" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B44">
         <f t="shared" ref="B44:H44" si="4">AVERAGE(B34:B43)</f>
@@ -21218,7 +20471,7 @@
         <v>17137.9401364</v>
       </c>
       <c r="L44" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M44">
         <f t="shared" ref="M44:S44" si="5">AVERAGE(M34:M43)</f>
@@ -21249,65 +20502,65 @@
         <v>10165.141580400001</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19">
       <c r="A47" t="s">
+        <v>33</v>
+      </c>
+      <c r="L47" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19">
+      <c r="A48" t="s">
+        <v>17</v>
+      </c>
+      <c r="B48" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" t="s">
         <v>19</v>
       </c>
-      <c r="L47" t="s">
+      <c r="D48" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>2</v>
-      </c>
-      <c r="B48" t="s">
-        <v>3</v>
-      </c>
-      <c r="C48" t="s">
-        <v>4</v>
-      </c>
-      <c r="D48" t="s">
-        <v>5</v>
-      </c>
       <c r="E48" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F48" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G48" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H48" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L48" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M48" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N48" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O48" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P48" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q48" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R48" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S48" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19">
       <c r="A49">
         <v>1</v>
       </c>
@@ -21357,7 +20610,7 @@
         <v>9173.6842219999999</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19">
       <c r="A50">
         <v>2</v>
       </c>
@@ -21407,7 +20660,7 @@
         <v>9170.2797630000005</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19">
       <c r="A51">
         <v>5</v>
       </c>
@@ -21457,7 +20710,7 @@
         <v>9149.9214929999998</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19">
       <c r="A52">
         <v>3</v>
       </c>
@@ -21507,7 +20760,7 @@
         <v>9167.4501650000002</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19">
       <c r="A53">
         <v>4</v>
       </c>
@@ -21557,7 +20810,7 @@
         <v>9138.2525330000008</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19">
       <c r="A54">
         <v>7</v>
       </c>
@@ -21607,7 +20860,7 @@
         <v>9131.5511669999996</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19">
       <c r="A55">
         <v>8</v>
       </c>
@@ -21657,7 +20910,7 @@
         <v>9134.6169140000002</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19">
       <c r="A56">
         <v>9</v>
       </c>
@@ -21707,7 +20960,7 @@
         <v>9131.9167070000003</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19">
       <c r="A57">
         <v>6</v>
       </c>
@@ -21757,7 +21010,7 @@
         <v>9133.6180490000006</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19">
       <c r="A58">
         <v>10</v>
       </c>
@@ -21807,9 +21060,9 @@
         <v>9147.7575749999996</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19">
       <c r="A59" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B59">
         <f t="shared" ref="B59:H59" si="6">AVERAGE(B49:B58)</f>
@@ -21840,7 +21093,7 @@
         <v>17125.123349299996</v>
       </c>
       <c r="L59" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M59">
         <f t="shared" ref="M59:S59" si="7">AVERAGE(M49:M58)</f>
@@ -21871,65 +21124,65 @@
         <v>9147.9048587999987</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19">
       <c r="A62" t="s">
+        <v>35</v>
+      </c>
+      <c r="L62" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19">
+      <c r="A63" t="s">
+        <v>17</v>
+      </c>
+      <c r="B63" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" t="s">
+        <v>19</v>
+      </c>
+      <c r="D63" t="s">
+        <v>20</v>
+      </c>
+      <c r="E63" t="s">
         <v>21</v>
       </c>
-      <c r="L62" t="s">
+      <c r="F63" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>2</v>
-      </c>
-      <c r="B63" t="s">
-        <v>3</v>
-      </c>
-      <c r="C63" t="s">
-        <v>4</v>
-      </c>
-      <c r="D63" t="s">
-        <v>5</v>
-      </c>
-      <c r="E63" t="s">
-        <v>6</v>
-      </c>
-      <c r="F63" t="s">
-        <v>7</v>
-      </c>
       <c r="G63" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H63" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L63" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M63" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N63" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O63" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P63" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q63" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R63" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S63" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19">
       <c r="A64">
         <v>5</v>
       </c>
@@ -21979,7 +21232,7 @@
         <v>8345.9417250000006</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19">
       <c r="A65">
         <v>1</v>
       </c>
@@ -22029,7 +21282,7 @@
         <v>8341.6171130000002</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19">
       <c r="A66">
         <v>2</v>
       </c>
@@ -22079,7 +21332,7 @@
         <v>8314.0962849999996</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19">
       <c r="A67">
         <v>4</v>
       </c>
@@ -22129,7 +21382,7 @@
         <v>8311.9814320000005</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19">
       <c r="A68">
         <v>3</v>
       </c>
@@ -22179,7 +21432,7 @@
         <v>8342.2389270000003</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19">
       <c r="A69">
         <v>6</v>
       </c>
@@ -22229,7 +21482,7 @@
         <v>8303.8883659999992</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19">
       <c r="A70">
         <v>7</v>
       </c>
@@ -22279,7 +21532,7 @@
         <v>8373.0291080000006</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19">
       <c r="A71">
         <v>8</v>
       </c>
@@ -22329,7 +21582,7 @@
         <v>8301.2626600000003</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19">
       <c r="A72">
         <v>9</v>
       </c>
@@ -22379,7 +21632,7 @@
         <v>8314.4486039999992</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19">
       <c r="A73">
         <v>10</v>
       </c>
@@ -22429,9 +21682,9 @@
         <v>8309.132877</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19">
       <c r="A74" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B74">
         <f t="shared" ref="B74:H74" si="8">AVERAGE(B64:B73)</f>
@@ -22462,7 +21715,7 @@
         <v>17209.3285101</v>
       </c>
       <c r="L74" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M74">
         <f t="shared" ref="M74:S74" si="9">AVERAGE(M64:M73)</f>
@@ -22493,65 +21746,65 @@
         <v>8325.7637097000006</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19">
       <c r="A77" t="s">
+        <v>37</v>
+      </c>
+      <c r="L77" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19">
+      <c r="A78" t="s">
+        <v>17</v>
+      </c>
+      <c r="B78" t="s">
+        <v>18</v>
+      </c>
+      <c r="C78" t="s">
+        <v>19</v>
+      </c>
+      <c r="D78" t="s">
+        <v>20</v>
+      </c>
+      <c r="E78" t="s">
+        <v>21</v>
+      </c>
+      <c r="F78" t="s">
+        <v>22</v>
+      </c>
+      <c r="G78" t="s">
         <v>23</v>
       </c>
-      <c r="L77" t="s">
+      <c r="H78" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>2</v>
-      </c>
-      <c r="B78" t="s">
-        <v>3</v>
-      </c>
-      <c r="C78" t="s">
-        <v>4</v>
-      </c>
-      <c r="D78" t="s">
-        <v>5</v>
-      </c>
-      <c r="E78" t="s">
-        <v>6</v>
-      </c>
-      <c r="F78" t="s">
-        <v>7</v>
-      </c>
-      <c r="G78" t="s">
-        <v>8</v>
-      </c>
-      <c r="H78" t="s">
-        <v>9</v>
-      </c>
       <c r="L78" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M78" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N78" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O78" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P78" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q78" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R78" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S78" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19">
       <c r="A79">
         <v>5</v>
       </c>
@@ -22601,7 +21854,7 @@
         <v>7657.6486500000001</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19">
       <c r="A80">
         <v>4</v>
       </c>
@@ -22651,7 +21904,7 @@
         <v>7655.1831659999998</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:19">
       <c r="A81">
         <v>2</v>
       </c>
@@ -22701,7 +21954,7 @@
         <v>7626.2264429999996</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:19">
       <c r="A82">
         <v>1</v>
       </c>
@@ -22751,7 +22004,7 @@
         <v>7615.5645439999998</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:19">
       <c r="A83">
         <v>3</v>
       </c>
@@ -22801,7 +22054,7 @@
         <v>7614.8120070000004</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:19">
       <c r="A84">
         <v>8</v>
       </c>
@@ -22851,7 +22104,7 @@
         <v>7618.0758020000003</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:19">
       <c r="A85">
         <v>9</v>
       </c>
@@ -22901,7 +22154,7 @@
         <v>7627.7174459999997</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:19">
       <c r="A86">
         <v>6</v>
       </c>
@@ -22951,7 +22204,7 @@
         <v>7607.9689719999997</v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:19">
       <c r="A87">
         <v>10</v>
       </c>
@@ -23001,7 +22254,7 @@
         <v>7607.1353079999999</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:19">
       <c r="A88">
         <v>7</v>
       </c>
@@ -23051,9 +22304,9 @@
         <v>7612.7463159999998</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:19">
       <c r="A89" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B89">
         <f t="shared" ref="B89:H89" si="10">AVERAGE(B79:B88)</f>
@@ -23084,7 +22337,7 @@
         <v>15229.421585500002</v>
       </c>
       <c r="L89" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M89">
         <f t="shared" ref="M89:S89" si="11">AVERAGE(M79:M88)</f>
@@ -23123,82 +22376,82 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A2:Z89"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>22</v>
+      </c>
+      <c r="R3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S3" t="s">
+        <v>24</v>
+      </c>
+      <c r="V3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" t="s">
-        <v>9</v>
-      </c>
-      <c r="L3" t="s">
-        <v>2</v>
-      </c>
-      <c r="M3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P3" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>7</v>
-      </c>
-      <c r="R3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S3" t="s">
-        <v>9</v>
-      </c>
-      <c r="V3" t="s">
-        <v>10</v>
-      </c>
       <c r="W3" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="X3" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="Y3" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="Z3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26">
       <c r="A4">
         <v>1</v>
       </c>
@@ -23267,7 +22520,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26">
       <c r="A5">
         <v>8</v>
       </c>
@@ -23336,7 +22589,7 @@
         <v>6.0000000000000012E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26">
       <c r="A6">
         <v>7</v>
       </c>
@@ -23405,7 +22658,7 @@
         <v>7.1000000000000008E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26">
       <c r="A7">
         <v>2</v>
       </c>
@@ -23474,7 +22727,7 @@
         <v>6.4000000000000015E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26">
       <c r="A8">
         <v>5</v>
       </c>
@@ -23543,7 +22796,7 @@
         <v>0.10300000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26">
       <c r="A9">
         <v>4</v>
       </c>
@@ -23612,7 +22865,7 @@
         <v>5.6000000000000008E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26">
       <c r="A10">
         <v>9</v>
       </c>
@@ -23681,7 +22934,7 @@
         <v>5.9000000000000011E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26">
       <c r="A11">
         <v>6</v>
       </c>
@@ -23750,7 +23003,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26">
       <c r="A12">
         <v>3</v>
       </c>
@@ -23819,7 +23072,7 @@
         <v>3.9999999999999994E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26">
       <c r="A13">
         <v>10</v>
       </c>
@@ -23888,9 +23141,9 @@
         <v>8.199999999999999E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B14">
         <f t="shared" ref="B14:H14" si="0">AVERAGE(B4:B13)</f>
@@ -23921,7 +23174,7 @@
         <v>17032.627661400002</v>
       </c>
       <c r="L14" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M14">
         <f t="shared" ref="M14:S14" si="1">AVERAGE(M4:M13)</f>
@@ -23971,7 +23224,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26">
       <c r="V15">
         <v>1536</v>
       </c>
@@ -23992,65 +23245,65 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="L17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
       <c r="A18" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D18" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F18" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G18" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H18" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L18" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M18" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N18" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O18" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P18" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q18" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R18" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
       <c r="A19">
         <v>7</v>
       </c>
@@ -24100,7 +23353,7 @@
         <v>11404.901334</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19">
       <c r="A20">
         <v>1</v>
       </c>
@@ -24150,7 +23403,7 @@
         <v>11405.601294</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19">
       <c r="A21">
         <v>8</v>
       </c>
@@ -24200,7 +23453,7 @@
         <v>11377.973341999999</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19">
       <c r="A22">
         <v>5</v>
       </c>
@@ -24250,7 +23503,7 @@
         <v>11376.768518000001</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19">
       <c r="A23">
         <v>4</v>
       </c>
@@ -24300,7 +23553,7 @@
         <v>11376.735984000001</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19">
       <c r="A24">
         <v>3</v>
       </c>
@@ -24350,7 +23603,7 @@
         <v>11377.29854</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19">
       <c r="A25">
         <v>2</v>
       </c>
@@ -24400,7 +23653,7 @@
         <v>11376.29657</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19">
       <c r="A26">
         <v>9</v>
       </c>
@@ -24450,7 +23703,7 @@
         <v>11377.161769</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19">
       <c r="A27">
         <v>6</v>
       </c>
@@ -24500,7 +23753,7 @@
         <v>11379.581152999999</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19">
       <c r="A28">
         <v>10</v>
       </c>
@@ -24550,9 +23803,9 @@
         <v>11377.414323999999</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19">
       <c r="A29" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B29">
         <f t="shared" ref="B29:H29" si="2">AVERAGE(B19:B28)</f>
@@ -24583,7 +23836,7 @@
         <v>17089.108096100001</v>
       </c>
       <c r="L29" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M29">
         <f t="shared" ref="M29:S29" si="3">AVERAGE(M19:M28)</f>
@@ -24614,65 +23867,65 @@
         <v>11382.9732828</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19">
       <c r="A32" t="s">
+        <v>31</v>
+      </c>
+      <c r="L32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19">
+      <c r="A33" t="s">
         <v>17</v>
       </c>
-      <c r="L32" t="s">
+      <c r="B33" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>2</v>
-      </c>
-      <c r="B33" t="s">
-        <v>3</v>
-      </c>
       <c r="C33" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D33" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E33" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F33" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G33" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H33" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L33" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M33" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N33" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O33" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P33" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q33" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R33" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S33" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19">
       <c r="A34">
         <v>4</v>
       </c>
@@ -24722,7 +23975,7 @@
         <v>10235.222827</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19">
       <c r="A35">
         <v>5</v>
       </c>
@@ -24772,7 +24025,7 @@
         <v>10236.916084</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19">
       <c r="A36">
         <v>2</v>
       </c>
@@ -24822,7 +24075,7 @@
         <v>10197.122648</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19">
       <c r="A37">
         <v>8</v>
       </c>
@@ -24872,7 +24125,7 @@
         <v>10196.690076000001</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19">
       <c r="A38">
         <v>1</v>
       </c>
@@ -24922,7 +24175,7 @@
         <v>10196.993275999999</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19">
       <c r="A39">
         <v>6</v>
       </c>
@@ -24972,7 +24225,7 @@
         <v>10197.102871999999</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19">
       <c r="A40">
         <v>7</v>
       </c>
@@ -25022,7 +24275,7 @@
         <v>10197.699524</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19">
       <c r="A41">
         <v>3</v>
       </c>
@@ -25072,7 +24325,7 @@
         <v>10197.142556999999</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19">
       <c r="A42">
         <v>9</v>
       </c>
@@ -25122,7 +24375,7 @@
         <v>10198.993087000001</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19">
       <c r="A43">
         <v>10</v>
       </c>
@@ -25172,9 +24425,9 @@
         <v>10198.679694</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19">
       <c r="A44" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B44">
         <f t="shared" ref="B44:H44" si="4">AVERAGE(B34:B43)</f>
@@ -25205,7 +24458,7 @@
         <v>17035.930061899999</v>
       </c>
       <c r="L44" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M44">
         <f t="shared" ref="M44:S44" si="5">AVERAGE(M34:M43)</f>
@@ -25236,65 +24489,65 @@
         <v>10205.2562645</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19">
       <c r="A47" t="s">
+        <v>33</v>
+      </c>
+      <c r="L47" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19">
+      <c r="A48" t="s">
+        <v>17</v>
+      </c>
+      <c r="B48" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" t="s">
         <v>19</v>
       </c>
-      <c r="L47" t="s">
+      <c r="D48" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>2</v>
-      </c>
-      <c r="B48" t="s">
-        <v>3</v>
-      </c>
-      <c r="C48" t="s">
-        <v>4</v>
-      </c>
-      <c r="D48" t="s">
-        <v>5</v>
-      </c>
       <c r="E48" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F48" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G48" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H48" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L48" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M48" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N48" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O48" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P48" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q48" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R48" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S48" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19">
       <c r="A49">
         <v>1</v>
       </c>
@@ -25344,7 +24597,7 @@
         <v>9283.5590269999993</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19">
       <c r="A50">
         <v>5</v>
       </c>
@@ -25394,7 +24647,7 @@
         <v>9282.0883680000006</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19">
       <c r="A51">
         <v>8</v>
       </c>
@@ -25444,7 +24697,7 @@
         <v>9228.0487429999994</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19">
       <c r="A52">
         <v>4</v>
       </c>
@@ -25494,7 +24747,7 @@
         <v>9228.1916079999992</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19">
       <c r="A53">
         <v>6</v>
       </c>
@@ -25544,7 +24797,7 @@
         <v>9227.5681029999996</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19">
       <c r="A54">
         <v>9</v>
       </c>
@@ -25594,7 +24847,7 @@
         <v>9228.5902000000006</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19">
       <c r="A55">
         <v>3</v>
       </c>
@@ -25644,7 +24897,7 @@
         <v>9227.8946959999994</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19">
       <c r="A56">
         <v>7</v>
       </c>
@@ -25694,7 +24947,7 @@
         <v>9228.1791150000008</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19">
       <c r="A57">
         <v>2</v>
       </c>
@@ -25744,7 +24997,7 @@
         <v>9227.0185409999995</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19">
       <c r="A58">
         <v>10</v>
       </c>
@@ -25794,9 +25047,9 @@
         <v>9226.601326</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19">
       <c r="A59" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B59">
         <f t="shared" ref="B59:H59" si="6">AVERAGE(B49:B58)</f>
@@ -25827,7 +25080,7 @@
         <v>17013.762679400003</v>
       </c>
       <c r="L59" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M59">
         <f t="shared" ref="M59:S59" si="7">AVERAGE(M49:M58)</f>
@@ -25858,65 +25111,65 @@
         <v>9238.7739727000007</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19">
       <c r="A62" t="s">
+        <v>35</v>
+      </c>
+      <c r="L62" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19">
+      <c r="A63" t="s">
+        <v>17</v>
+      </c>
+      <c r="B63" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" t="s">
+        <v>19</v>
+      </c>
+      <c r="D63" t="s">
+        <v>20</v>
+      </c>
+      <c r="E63" t="s">
         <v>21</v>
       </c>
-      <c r="L62" t="s">
+      <c r="F63" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>2</v>
-      </c>
-      <c r="B63" t="s">
-        <v>3</v>
-      </c>
-      <c r="C63" t="s">
-        <v>4</v>
-      </c>
-      <c r="D63" t="s">
-        <v>5</v>
-      </c>
-      <c r="E63" t="s">
-        <v>6</v>
-      </c>
-      <c r="F63" t="s">
-        <v>7</v>
-      </c>
       <c r="G63" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H63" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L63" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M63" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N63" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O63" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P63" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q63" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R63" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S63" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19">
       <c r="A64">
         <v>5</v>
       </c>
@@ -25966,7 +25219,7 @@
         <v>8496.358397</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19">
       <c r="A65">
         <v>2</v>
       </c>
@@ -26016,7 +25269,7 @@
         <v>8494.8060929999992</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19">
       <c r="A66">
         <v>4</v>
       </c>
@@ -26066,7 +25319,7 @@
         <v>8435.0403380000007</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19">
       <c r="A67">
         <v>7</v>
       </c>
@@ -26116,7 +25369,7 @@
         <v>8434.7813229999992</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19">
       <c r="A68">
         <v>3</v>
       </c>
@@ -26166,7 +25419,7 @@
         <v>8433.0137739999991</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19">
       <c r="A69">
         <v>1</v>
       </c>
@@ -26216,7 +25469,7 @@
         <v>8432.9651680000006</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19">
       <c r="A70">
         <v>10</v>
       </c>
@@ -26266,7 +25519,7 @@
         <v>8433.5755239999999</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19">
       <c r="A71">
         <v>6</v>
       </c>
@@ -26316,7 +25569,7 @@
         <v>8433.8455959999992</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19">
       <c r="A72">
         <v>9</v>
       </c>
@@ -26366,7 +25619,7 @@
         <v>8433.3775370000003</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19">
       <c r="A73">
         <v>8</v>
       </c>
@@ -26416,9 +25669,9 @@
         <v>8432.7725709999995</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19">
       <c r="A74" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B74">
         <f t="shared" ref="B74:H74" si="8">AVERAGE(B64:B73)</f>
@@ -26449,7 +25702,7 @@
         <v>17019.624936</v>
       </c>
       <c r="L74" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M74">
         <f t="shared" ref="M74:S74" si="9">AVERAGE(M64:M73)</f>
@@ -26480,65 +25733,65 @@
         <v>8446.0536321</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19">
       <c r="A77" t="s">
+        <v>37</v>
+      </c>
+      <c r="L77" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19">
+      <c r="A78" t="s">
+        <v>17</v>
+      </c>
+      <c r="B78" t="s">
+        <v>18</v>
+      </c>
+      <c r="C78" t="s">
+        <v>19</v>
+      </c>
+      <c r="D78" t="s">
+        <v>20</v>
+      </c>
+      <c r="E78" t="s">
+        <v>21</v>
+      </c>
+      <c r="F78" t="s">
+        <v>22</v>
+      </c>
+      <c r="G78" t="s">
         <v>23</v>
       </c>
-      <c r="L77" t="s">
+      <c r="H78" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>2</v>
-      </c>
-      <c r="B78" t="s">
-        <v>3</v>
-      </c>
-      <c r="C78" t="s">
-        <v>4</v>
-      </c>
-      <c r="D78" t="s">
-        <v>5</v>
-      </c>
-      <c r="E78" t="s">
-        <v>6</v>
-      </c>
-      <c r="F78" t="s">
-        <v>7</v>
-      </c>
-      <c r="G78" t="s">
-        <v>8</v>
-      </c>
-      <c r="H78" t="s">
-        <v>9</v>
-      </c>
       <c r="L78" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M78" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N78" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O78" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P78" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q78" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R78" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S78" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19">
       <c r="A79">
         <v>4</v>
       </c>
@@ -26588,7 +25841,7 @@
         <v>7537.702757</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19">
       <c r="A80">
         <v>1</v>
       </c>
@@ -26638,7 +25891,7 @@
         <v>7538.6600639999997</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:19">
       <c r="A81">
         <v>3</v>
       </c>
@@ -26688,7 +25941,7 @@
         <v>7460.291193</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:19">
       <c r="A82">
         <v>7</v>
       </c>
@@ -26738,7 +25991,7 @@
         <v>7459.2908129999996</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:19">
       <c r="A83">
         <v>2</v>
       </c>
@@ -26788,7 +26041,7 @@
         <v>7458.34879</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:19">
       <c r="A84">
         <v>8</v>
       </c>
@@ -26838,7 +26091,7 @@
         <v>7458.7026679999999</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:19">
       <c r="A85">
         <v>6</v>
       </c>
@@ -26888,7 +26141,7 @@
         <v>7459.5881499999996</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:19">
       <c r="A86">
         <v>9</v>
       </c>
@@ -26938,7 +26191,7 @@
         <v>7458.0290299999997</v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:19">
       <c r="A87">
         <v>5</v>
       </c>
@@ -26988,7 +26241,7 @@
         <v>7459.5499579999996</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:19">
       <c r="A88">
         <v>10</v>
       </c>
@@ -27038,9 +26291,9 @@
         <v>7459.9256539999997</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:19">
       <c r="A89" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B89">
         <f t="shared" ref="B89:H89" si="10">AVERAGE(B79:B88)</f>
@@ -27071,7 +26324,7 @@
         <v>14830.405445300003</v>
       </c>
       <c r="L89" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M89">
         <f t="shared" ref="M89:S89" si="11">AVERAGE(M79:M88)</f>
